--- a/Coleções/Coleção 1 - Goku/avaliacao_colecao1.xlsx
+++ b/Coleções/Coleção 1 - Goku/avaliacao_colecao1.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[a gerar]</t>
+          <t>tentativa 4 - Alucard(SoTN).jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[a gerar]</t>
+          <t>tentativa 5 - Alucard(SoTN).jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[a gerar]</t>
+          <t>tentativa 2 - LF GBA sprite artist - Requests - Fire Emble.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[a gerar]</t>
+          <t>tentativa 3 - LF GBA sprite artist - Requests - Fire Emble.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4035,6 +4035,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
